--- a/Cronometragem_QRCode.xlsx
+++ b/Cronometragem_QRCode.xlsx
@@ -124,7 +124,7 @@
     <t xml:space="preserve">Custo da hora do mecânico (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">citar a fonte no documento</t>
+    <t xml:space="preserve">R$ 3.150/mês ÷ 220 h – Portal Salário/Novo Caged, CBO 9113-05</t>
   </si>
   <si>
     <t xml:space="preserve">Tempo ganho por intervenção (s)</t>
@@ -864,7 +864,9 @@
       <c r="A10" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4"/>
+      <c r="B10" s="4" t="n">
+        <v>14.32</v>
+      </c>
       <c r="C10" s="0" t="s">
         <v>33</v>
       </c>
